--- a/examples/jon+jane.xlsx
+++ b/examples/jon+jane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Dropbox\Retirement\MyProject\Owl\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44774331-1297-4241-8A50-0F91B3B4B8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AEA0CC-505D-4F7D-8E6E-032FD8997678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="1310" windowWidth="14400" windowHeight="8170" xr2:uid="{10BCA99F-290D-43B0-90F7-A2A56377E151}"/>
+    <workbookView xWindow="-21240" yWindow="15780" windowWidth="15045" windowHeight="11700" xr2:uid="{10BCA99F-290D-43B0-90F7-A2A56377E151}"/>
   </bookViews>
   <sheets>
     <sheet name="Jon" sheetId="1" r:id="rId1"/>
@@ -428,25 +428,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB57614-FCF1-4139-AA0D-31AF55A08D66}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -475,168 +475,167 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2025</v>
-      </c>
-      <c r="B2" s="1">
-        <v>120000</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D2" s="1">
-        <v>7000</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="1">
-        <v>120000</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D3" s="1">
-        <v>7000</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2027</v>
-      </c>
-      <c r="B4" s="1">
-        <v>120000</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="1">
-        <v>7000</v>
-      </c>
+        <v>2022</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2028</v>
-      </c>
-      <c r="B5" s="1">
-        <v>120000</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D5" s="1">
-        <v>7000</v>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2029</v>
-      </c>
-      <c r="B6" s="1">
-        <v>120000</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="1">
-        <v>7000</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2030</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+        <v>2025</v>
+      </c>
+      <c r="B7" s="1">
+        <v>120000</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7000</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2031</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+        <v>2026</v>
+      </c>
+      <c r="B8" s="1">
+        <v>120000</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7000</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2032</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+        <v>2027</v>
+      </c>
+      <c r="B9" s="1">
+        <v>120000</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7000</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2033</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+        <v>2028</v>
+      </c>
+      <c r="B10" s="1">
+        <v>120000</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7000</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2034</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+        <v>2029</v>
+      </c>
+      <c r="B11" s="1">
+        <v>120000</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D11" s="1">
+        <v>7000</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -647,9 +646,9 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -660,9 +659,9 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -673,9 +672,9 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -686,9 +685,9 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -699,9 +698,9 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -712,9 +711,9 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -725,9 +724,9 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -738,9 +737,9 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -751,9 +750,9 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -764,9 +763,9 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -777,9 +776,9 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -790,9 +789,9 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -803,9 +802,9 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -816,9 +815,9 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -829,9 +828,9 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -842,9 +841,9 @@
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -855,9 +854,9 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -868,9 +867,9 @@
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -881,9 +880,9 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -894,8 +893,73 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>2050</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2051</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2052</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2053</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2054</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>2055</v>
       </c>
     </row>
@@ -907,21 +971,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DE7EE4-731B-47FB-9A4E-667972814602}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -950,94 +1014,83 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2025</v>
-      </c>
-      <c r="B2" s="1">
-        <v>80000</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1">
-        <v>3000</v>
-      </c>
+      <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1">
+        <v>6000</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="1">
-        <v>80000</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="1">
-        <v>3000</v>
-      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="G3" s="1">
+        <v>6000</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2027</v>
-      </c>
-      <c r="B4" s="1">
-        <v>80000</v>
-      </c>
+        <v>2022</v>
+      </c>
+      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="1">
-        <v>3000</v>
-      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1">
+        <v>6000</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2028</v>
-      </c>
-      <c r="B5" s="1">
-        <v>80000</v>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="1">
-        <v>3000</v>
-      </c>
+      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>7000</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2029</v>
-      </c>
-      <c r="B6" s="1">
-        <v>80000</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1">
-        <v>3000</v>
-      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>7500</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="1">
         <v>80000</v>
@@ -1052,9 +1105,9 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B8" s="1">
         <v>80000</v>
@@ -1069,9 +1122,9 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="B9" s="1">
         <v>80000</v>
@@ -1086,74 +1139,94 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2033</v>
-      </c>
-      <c r="B10" s="1"/>
+        <v>2028</v>
+      </c>
+      <c r="B10" s="1">
+        <v>80000</v>
+      </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1">
+        <v>3000</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2034</v>
-      </c>
-      <c r="B11" s="1"/>
+        <v>2029</v>
+      </c>
+      <c r="B11" s="1">
+        <v>80000</v>
+      </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1">
+        <v>3000</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2035</v>
-      </c>
-      <c r="B12" s="1"/>
+        <v>2030</v>
+      </c>
+      <c r="B12" s="1">
+        <v>80000</v>
+      </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <v>3000</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2036</v>
-      </c>
-      <c r="B13" s="1"/>
+        <v>2031</v>
+      </c>
+      <c r="B13" s="1">
+        <v>80000</v>
+      </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1">
+        <v>3000</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2037</v>
-      </c>
-      <c r="B14" s="1"/>
+        <v>2032</v>
+      </c>
+      <c r="B14" s="1">
+        <v>80000</v>
+      </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1">
+        <v>3000</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1164,9 +1237,9 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1177,9 +1250,9 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1190,9 +1263,9 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1203,9 +1276,9 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1216,9 +1289,9 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1229,9 +1302,9 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1242,9 +1315,9 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1255,9 +1328,9 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1268,9 +1341,9 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1281,9 +1354,9 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1294,9 +1367,9 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1307,9 +1380,9 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1320,9 +1393,9 @@
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1333,9 +1406,9 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1346,9 +1419,9 @@
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1359,9 +1432,9 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1372,9 +1445,9 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1385,9 +1458,9 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2056</v>
+        <v>2051</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1398,13 +1471,78 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
+        <v>2052</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2053</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2054</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2055</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2056</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>2057</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>2058</v>
       </c>
     </row>
